--- a/data/Mar/19-03-2026/NGAY 19-03.xlsx
+++ b/data/Mar/19-03-2026/NGAY 19-03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\19-03-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9F6F40-619A-4803-B7DC-AE854C602EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC497523-A220-4DBE-8338-5B6C33DAA5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B6C9D35-2D77-4262-A067-18EED5C7F01A}"/>
   </bookViews>
